--- a/Data_clean/MCAS/Estados_US/Edos_USA_2021/SOUTH_DAKOTA_2021.xlsx
+++ b/Data_clean/MCAS/Estados_US/Edos_USA_2021/SOUTH_DAKOTA_2021.xlsx
@@ -351,28 +351,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D184"/>
+  <dimension ref="A1:D178"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
@@ -395,6 +395,11 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>Calvillo</t>
@@ -408,6 +413,11 @@
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>Jesús María</t>
@@ -421,9 +431,14 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Rincón de Romos</t>
+          <t>Rincón De Romos</t>
         </is>
       </c>
       <c r="C5">
@@ -434,6 +449,11 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>Total</t>
@@ -465,6 +485,11 @@
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>Tijuana</t>
@@ -478,6 +503,11 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>Total</t>
@@ -509,6 +539,11 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>Total</t>
@@ -540,6 +575,11 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>Cintalapa</t>
@@ -553,6 +593,11 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>La Trinitaria</t>
@@ -566,6 +611,11 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>Las Margaritas</t>
@@ -579,6 +629,11 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>Mapastepec</t>
@@ -592,6 +647,11 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>Pijijiapan</t>
@@ -605,6 +665,11 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>Total</t>
@@ -636,6 +701,11 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>Namiquipa</t>
@@ -649,6 +719,11 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>Nuevo Casas Grandes</t>
@@ -662,6 +737,11 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>Total</t>
@@ -693,6 +773,11 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>Total</t>
@@ -724,6 +809,11 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>Total</t>
@@ -739,7 +829,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Ciudad de México</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -755,6 +845,11 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>Benito Juárez</t>
@@ -768,6 +863,11 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>Cuauhtémoc</t>
@@ -781,6 +881,11 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>Iztacalco</t>
@@ -794,6 +899,11 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>Miguel Hidalgo</t>
@@ -807,6 +917,11 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>Total</t>
@@ -838,6 +953,11 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>Vicente Guerrero</t>
@@ -851,6 +971,11 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
           <t>Total</t>
@@ -866,12 +991,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Estado de México</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ecatepec de Morelos</t>
+          <t>Ecatepec De Morelos</t>
         </is>
       </c>
       <c r="C36">
@@ -882,6 +1007,11 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>La Paz</t>
@@ -895,9 +1025,14 @@
       </c>
     </row>
     <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>San Felipe del Progreso</t>
+          <t>San Felipe Del Progreso</t>
         </is>
       </c>
       <c r="C38">
@@ -908,6 +1043,11 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>Timilpan</t>
@@ -921,6 +1061,11 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>Toluca</t>
@@ -934,6 +1079,11 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>Villa Guerrero</t>
@@ -947,6 +1097,11 @@
       </c>
     </row>
     <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
           <t>Villa Victoria</t>
@@ -960,6 +1115,11 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>Total</t>
@@ -991,6 +1151,11 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
           <t>Irapuato</t>
@@ -1004,6 +1169,11 @@
       </c>
     </row>
     <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr">
         <is>
           <t>León</t>
@@ -1017,6 +1187,11 @@
       </c>
     </row>
     <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>Ocampo</t>
@@ -1030,6 +1205,11 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
           <t>San Felipe</t>
@@ -1043,9 +1223,14 @@
       </c>
     </row>
     <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>San Francisco del Rincón</t>
+          <t>San Francisco Del Rincón</t>
         </is>
       </c>
       <c r="C49">
@@ -1056,6 +1241,11 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1076,7 +1266,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Acapulco de Juárez</t>
+          <t>Acapulco De Juárez</t>
         </is>
       </c>
       <c r="C51">
@@ -1087,6 +1277,11 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>Ahuacuotzingo</t>
@@ -1100,6 +1295,11 @@
       </c>
     </row>
     <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
           <t>Alpoyeca</t>
@@ -1113,9 +1313,14 @@
       </c>
     </row>
     <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Atenango del Río</t>
+          <t>Atenango Del Río</t>
         </is>
       </c>
       <c r="C54">
@@ -1126,6 +1331,11 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>Azoyú</t>
@@ -1139,6 +1349,11 @@
       </c>
     </row>
     <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
           <t>Copalillo</t>
@@ -1152,9 +1367,14 @@
       </c>
     </row>
     <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Huitzuco de los Figueroa</t>
+          <t>Huitzuco De Los Figueroa</t>
         </is>
       </c>
       <c r="C57">
@@ -1165,9 +1385,14 @@
       </c>
     </row>
     <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Iguala de la Independencia</t>
+          <t>Iguala De La Independencia</t>
         </is>
       </c>
       <c r="C58">
@@ -1178,9 +1403,14 @@
       </c>
     </row>
     <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Zihuatanejo de Azueta</t>
+          <t>Zihuatanejo De Azueta</t>
         </is>
       </c>
       <c r="C59">
@@ -1191,6 +1421,11 @@
       </c>
     </row>
     <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
           <t>Petatlán</t>
@@ -1204,6 +1439,11 @@
       </c>
     </row>
     <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
           <t>Quechultenango</t>
@@ -1217,6 +1457,11 @@
       </c>
     </row>
     <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
           <t>San Marcos</t>
@@ -1230,6 +1475,11 @@
       </c>
     </row>
     <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
           <t>San Miguel Totolapan</t>
@@ -1243,9 +1493,14 @@
       </c>
     </row>
     <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Taxco de Alarcón</t>
+          <t>Taxco De Alarcón</t>
         </is>
       </c>
       <c r="C64">
@@ -1256,9 +1511,14 @@
       </c>
     </row>
     <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Técpan de Galeana</t>
+          <t>Técpan De Galeana</t>
         </is>
       </c>
       <c r="C65">
@@ -1269,6 +1529,11 @@
       </c>
     </row>
     <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
           <t>Zirándaro</t>
@@ -1282,6 +1547,11 @@
       </c>
     </row>
     <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1302,7 +1572,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Cuautepec de Hinojosa</t>
+          <t>Cuautepec De Hinojosa</t>
         </is>
       </c>
       <c r="C68">
@@ -1313,9 +1583,14 @@
       </c>
     </row>
     <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Huasca de Ocampo</t>
+          <t>Huasca De Ocampo</t>
         </is>
       </c>
       <c r="C69">
@@ -1326,6 +1601,11 @@
       </c>
     </row>
     <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
           <t>Jaltocán</t>
@@ -1339,9 +1619,14 @@
       </c>
     </row>
     <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Tezontepec de Aldama</t>
+          <t>Tezontepec De Aldama</t>
         </is>
       </c>
       <c r="C71">
@@ -1352,9 +1637,14 @@
       </c>
     </row>
     <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Tulancingo de Bravo</t>
+          <t>Tulancingo De Bravo</t>
         </is>
       </c>
       <c r="C72">
@@ -1365,6 +1655,11 @@
       </c>
     </row>
     <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1396,9 +1691,14 @@
       </c>
     </row>
     <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Autlán de Navarro</t>
+          <t>Autlán De Navarro</t>
         </is>
       </c>
       <c r="C75">
@@ -1409,6 +1709,11 @@
       </c>
     </row>
     <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
           <t>Ayutla</t>
@@ -1422,6 +1727,11 @@
       </c>
     </row>
     <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
           <t>Degollado</t>
@@ -1435,6 +1745,11 @@
       </c>
     </row>
     <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
           <t>El Arenal</t>
@@ -1448,6 +1763,11 @@
       </c>
     </row>
     <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B79" t="inlineStr">
         <is>
           <t>Gómez Farías</t>
@@ -1461,6 +1781,11 @@
       </c>
     </row>
     <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
           <t>Guadalajara</t>
@@ -1474,9 +1799,14 @@
       </c>
     </row>
     <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Lagos de Moreno</t>
+          <t>Lagos De Moreno</t>
         </is>
       </c>
       <c r="C81">
@@ -1487,6 +1817,11 @@
       </c>
     </row>
     <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B82" t="inlineStr">
         <is>
           <t>Poncitlán</t>
@@ -1500,6 +1835,11 @@
       </c>
     </row>
     <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B83" t="inlineStr">
         <is>
           <t>Puerto Vallarta</t>
@@ -1513,9 +1853,14 @@
       </c>
     </row>
     <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>San Diego de Alejandría</t>
+          <t>San Diego De Alejandría</t>
         </is>
       </c>
       <c r="C84">
@@ -1526,9 +1871,14 @@
       </c>
     </row>
     <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>San Miguel el Alto</t>
+          <t>San Miguel El Alto</t>
         </is>
       </c>
       <c r="C85">
@@ -1539,6 +1889,11 @@
       </c>
     </row>
     <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B86" t="inlineStr">
         <is>
           <t>Tala</t>
@@ -1552,9 +1907,14 @@
       </c>
     </row>
     <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Tlajomulco de Zúñiga</t>
+          <t>Tlajomulco De Zúñiga</t>
         </is>
       </c>
       <c r="C87">
@@ -1565,6 +1925,11 @@
       </c>
     </row>
     <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B88" t="inlineStr">
         <is>
           <t>Zapotiltic</t>
@@ -1578,6 +1943,11 @@
       </c>
     </row>
     <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B89" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1587,7 +1957,7 @@
         <v>22</v>
       </c>
       <c r="D89">
-        <v>0.09090909090909091</v>
+        <v>0.09090909090909093</v>
       </c>
     </row>
     <row r="90">
@@ -1609,6 +1979,11 @@
       </c>
     </row>
     <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B91" t="inlineStr">
         <is>
           <t>Aquila</t>
@@ -1622,6 +1997,11 @@
       </c>
     </row>
     <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B92" t="inlineStr">
         <is>
           <t>Jungapeo</t>
@@ -1635,6 +2015,11 @@
       </c>
     </row>
     <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B93" t="inlineStr">
         <is>
           <t>La Piedad</t>
@@ -1648,6 +2033,11 @@
       </c>
     </row>
     <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B94" t="inlineStr">
         <is>
           <t>Lázaro Cárdenas</t>
@@ -1661,6 +2051,11 @@
       </c>
     </row>
     <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B95" t="inlineStr">
         <is>
           <t>Maravatío</t>
@@ -1674,6 +2069,11 @@
       </c>
     </row>
     <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B96" t="inlineStr">
         <is>
           <t>Morelia</t>
@@ -1687,6 +2087,11 @@
       </c>
     </row>
     <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B97" t="inlineStr">
         <is>
           <t>Purépero</t>
@@ -1700,6 +2105,11 @@
       </c>
     </row>
     <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B98" t="inlineStr">
         <is>
           <t>Puruándiro</t>
@@ -1713,6 +2123,11 @@
       </c>
     </row>
     <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B99" t="inlineStr">
         <is>
           <t>Tarímbaro</t>
@@ -1726,6 +2141,11 @@
       </c>
     </row>
     <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B100" t="inlineStr">
         <is>
           <t>Tuxpan</t>
@@ -1739,6 +2159,11 @@
       </c>
     </row>
     <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B101" t="inlineStr">
         <is>
           <t>Zinapécuaro</t>
@@ -1752,6 +2177,11 @@
       </c>
     </row>
     <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B102" t="inlineStr">
         <is>
           <t>Zitácuaro</t>
@@ -1765,6 +2195,11 @@
       </c>
     </row>
     <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B103" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1796,6 +2231,11 @@
       </c>
     </row>
     <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B105" t="inlineStr">
         <is>
           <t>Yautepec</t>
@@ -1809,6 +2249,11 @@
       </c>
     </row>
     <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B106" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1840,6 +2285,11 @@
       </c>
     </row>
     <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B108" t="inlineStr">
         <is>
           <t>San Blas</t>
@@ -1853,6 +2303,11 @@
       </c>
     </row>
     <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B109" t="inlineStr">
         <is>
           <t>San Pedro Lagunillas</t>
@@ -1866,6 +2321,11 @@
       </c>
     </row>
     <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B110" t="inlineStr">
         <is>
           <t>Santiago Ixcuintla</t>
@@ -1879,6 +2339,11 @@
       </c>
     </row>
     <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B111" t="inlineStr">
         <is>
           <t>Tuxpan</t>
@@ -1892,6 +2357,11 @@
       </c>
     </row>
     <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B112" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1912,7 +2382,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Acatlán de Pérez Figueroa</t>
+          <t>Acatlán De Pérez Figueroa</t>
         </is>
       </c>
       <c r="C113">
@@ -1923,6 +2393,11 @@
       </c>
     </row>
     <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B114" t="inlineStr">
         <is>
           <t>Chahuites</t>
@@ -1936,9 +2411,14 @@
       </c>
     </row>
     <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Heroica Ciudad de Huajuapan de León</t>
+          <t>Heroica Ciudad De Huajuapan De León</t>
         </is>
       </c>
       <c r="C115">
@@ -1949,6 +2429,11 @@
       </c>
     </row>
     <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B116" t="inlineStr">
         <is>
           <t>Loma Bonita</t>
@@ -1962,6 +2447,11 @@
       </c>
     </row>
     <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B117" t="inlineStr">
         <is>
           <t>Matías Romero Avendaño</t>
@@ -1975,6 +2465,11 @@
       </c>
     </row>
     <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B118" t="inlineStr">
         <is>
           <t>San Juan Bautista Tuxtepec</t>
@@ -1988,6 +2483,11 @@
       </c>
     </row>
     <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B119" t="inlineStr">
         <is>
           <t>San Lorenzo Texmelúcan</t>
@@ -2001,6 +2501,11 @@
       </c>
     </row>
     <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B120" t="inlineStr">
         <is>
           <t>San Pedro Tapanatepec</t>
@@ -2014,6 +2519,11 @@
       </c>
     </row>
     <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B121" t="inlineStr">
         <is>
           <t>Santo Domingo Tonalá</t>
@@ -2027,6 +2537,11 @@
       </c>
     </row>
     <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B122" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2058,9 +2573,14 @@
       </c>
     </row>
     <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Cuetzalan del Progreso</t>
+          <t>Cuetzalan Del Progreso</t>
         </is>
       </c>
       <c r="C124">
@@ -2071,9 +2591,14 @@
       </c>
     </row>
     <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Huitzilan de Serdán</t>
+          <t>Huitzilan De Serdán</t>
         </is>
       </c>
       <c r="C125">
@@ -2084,6 +2609,11 @@
       </c>
     </row>
     <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B126" t="inlineStr">
         <is>
           <t>Quimixtlán</t>
@@ -2097,6 +2627,11 @@
       </c>
     </row>
     <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B127" t="inlineStr">
         <is>
           <t>San Martín Texmelucan</t>
@@ -2110,9 +2645,14 @@
       </c>
     </row>
     <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Tetela de Ocampo</t>
+          <t>Tetela De Ocampo</t>
         </is>
       </c>
       <c r="C128">
@@ -2123,6 +2663,11 @@
       </c>
     </row>
     <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B129" t="inlineStr">
         <is>
           <t>Tlatlauquitepec</t>
@@ -2136,6 +2681,11 @@
       </c>
     </row>
     <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B130" t="inlineStr">
         <is>
           <t>Zacatlán</t>
@@ -2149,6 +2699,11 @@
       </c>
     </row>
     <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B131" t="inlineStr">
         <is>
           <t>Zaragoza</t>
@@ -2162,6 +2717,11 @@
       </c>
     </row>
     <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B132" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2182,7 +2742,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>San Juan del Río</t>
+          <t>San Juan Del Río</t>
         </is>
       </c>
       <c r="C133">
@@ -2193,6 +2753,11 @@
       </c>
     </row>
     <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B134" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2224,6 +2789,11 @@
       </c>
     </row>
     <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B136" t="inlineStr">
         <is>
           <t>Ciudad Fernández</t>
@@ -2237,6 +2807,11 @@
       </c>
     </row>
     <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B137" t="inlineStr">
         <is>
           <t>Ebano</t>
@@ -2250,6 +2825,11 @@
       </c>
     </row>
     <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B138" t="inlineStr">
         <is>
           <t>Matehuala</t>
@@ -2263,6 +2843,11 @@
       </c>
     </row>
     <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B139" t="inlineStr">
         <is>
           <t>Salinas</t>
@@ -2276,6 +2861,11 @@
       </c>
     </row>
     <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B140" t="inlineStr">
         <is>
           <t>Santo Domingo</t>
@@ -2289,6 +2879,11 @@
       </c>
     </row>
     <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B141" t="inlineStr">
         <is>
           <t>Vanegas</t>
@@ -2302,6 +2897,11 @@
       </c>
     </row>
     <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B142" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2333,6 +2933,11 @@
       </c>
     </row>
     <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B144" t="inlineStr">
         <is>
           <t>Culiacán</t>
@@ -2346,6 +2951,11 @@
       </c>
     </row>
     <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B145" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2377,6 +2987,11 @@
       </c>
     </row>
     <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B147" t="inlineStr">
         <is>
           <t>Huatabampo</t>
@@ -2390,6 +3005,11 @@
       </c>
     </row>
     <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B148" t="inlineStr">
         <is>
           <t>Nogales</t>
@@ -2403,6 +3023,11 @@
       </c>
     </row>
     <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B149" t="inlineStr">
         <is>
           <t>Sahuaripa</t>
@@ -2416,6 +3041,11 @@
       </c>
     </row>
     <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B150" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2447,6 +3077,11 @@
       </c>
     </row>
     <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B152" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2478,6 +3113,11 @@
       </c>
     </row>
     <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B154" t="inlineStr">
         <is>
           <t>El Mante</t>
@@ -2491,6 +3131,11 @@
       </c>
     </row>
     <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B155" t="inlineStr">
         <is>
           <t>Tampico</t>
@@ -2504,6 +3149,11 @@
       </c>
     </row>
     <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B156" t="inlineStr">
         <is>
           <t>Tula</t>
@@ -2517,6 +3167,11 @@
       </c>
     </row>
     <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B157" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2537,7 +3192,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Cosamaloapan de Carpio</t>
+          <t>Cosamaloapan De Carpio</t>
         </is>
       </c>
       <c r="C158">
@@ -2548,9 +3203,14 @@
       </c>
     </row>
     <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Cosautlán de Carvajal</t>
+          <t>Cosautlán De Carvajal</t>
         </is>
       </c>
       <c r="C159">
@@ -2561,6 +3221,11 @@
       </c>
     </row>
     <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B160" t="inlineStr">
         <is>
           <t>Coscomatepec</t>
@@ -2574,6 +3239,11 @@
       </c>
     </row>
     <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B161" t="inlineStr">
         <is>
           <t>Manlio Fabio Altamirano</t>
@@ -2587,6 +3257,11 @@
       </c>
     </row>
     <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B162" t="inlineStr">
         <is>
           <t>Misantla</t>
@@ -2600,6 +3275,11 @@
       </c>
     </row>
     <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B163" t="inlineStr">
         <is>
           <t>Omealca</t>
@@ -2613,9 +3293,14 @@
       </c>
     </row>
     <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Soledad de Doblado</t>
+          <t>Soledad De Doblado</t>
         </is>
       </c>
       <c r="C164">
@@ -2626,6 +3311,11 @@
       </c>
     </row>
     <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B165" t="inlineStr">
         <is>
           <t>Tezonapa</t>
@@ -2639,6 +3329,11 @@
       </c>
     </row>
     <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B166" t="inlineStr">
         <is>
           <t>Tierra Blanca</t>
@@ -2652,9 +3347,14 @@
       </c>
     </row>
     <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Vega de Alatorre</t>
+          <t>Vega De Alatorre</t>
         </is>
       </c>
       <c r="C167">
@@ -2665,6 +3365,11 @@
       </c>
     </row>
     <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B168" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2696,6 +3401,11 @@
       </c>
     </row>
     <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B170" t="inlineStr">
         <is>
           <t>Jerez</t>
@@ -2709,6 +3419,11 @@
       </c>
     </row>
     <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B171" t="inlineStr">
         <is>
           <t>Río Grande</t>
@@ -2722,6 +3437,11 @@
       </c>
     </row>
     <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B172" t="inlineStr">
         <is>
           <t>Sombrerete</t>
@@ -2735,6 +3455,11 @@
       </c>
     </row>
     <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B173" t="inlineStr">
         <is>
           <t>Tepetongo</t>
@@ -2748,6 +3473,11 @@
       </c>
     </row>
     <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B174" t="inlineStr">
         <is>
           <t>Valparaíso</t>
@@ -2761,9 +3491,14 @@
       </c>
     </row>
     <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Villa de Cos</t>
+          <t>Villa De Cos</t>
         </is>
       </c>
       <c r="C175">
@@ -2774,6 +3509,11 @@
       </c>
     </row>
     <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B176" t="inlineStr">
         <is>
           <t>Zacatecas</t>
@@ -2787,6 +3527,11 @@
       </c>
     </row>
     <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B177" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2810,41 +3555,6 @@
       </c>
       <c r="D178">
         <v>1</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 701,861</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>Mayo de 2022</t>
-        </is>
       </c>
     </row>
   </sheetData>
